--- a/Trắc nghiệm ôn luyện/BA Functional/multiple_choice_sample_template_REQUIREMENT_ELICITATION.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Functional/multiple_choice_sample_template_REQUIREMENT_ELICITATION.xlsx
@@ -453,19 +453,19 @@
         <v>Yêu cầu chức năng định nghĩa các hành vi, dịch vụ hoặc chức năng cụ thể mà hệ thống phần mềm phải thực hiện khi vận hành.</v>
       </c>
       <c r="E2" t="str">
+        <v>Các tiêu chuẩn về hiệu năng, bảo mật và tính khả dụng — quy định ràng buộc phi chức năng của hệ thống</v>
+      </c>
+      <c r="F2" t="str">
         <v>Những gì hệ thống phải thực hiện và cung cấp cho người dùng — quy định chức năng nghiệp vụ cụ thể</v>
       </c>
-      <c r="F2" t="str">
-        <v>Các tiêu chuẩn về hiệu năng, bảo mật và tính khả dụng — quy định ràng buộc phi chức năng của hệ thống</v>
-      </c>
       <c r="G2" t="str">
+        <v>Thời gian và ngân sách cần thiết để hoàn thành dự án — quy định các ràng buộc về mặt quản lý dự án</v>
+      </c>
+      <c r="H2" t="str">
         <v>Công nghệ và ngôn ngữ lập trình được sử dụng để phát triển — quy định giới hạn triển khai của dự án</v>
       </c>
-      <c r="H2" t="str">
-        <v>Thời gian và ngân sách cần thiết để hoàn thành dự án — quy định các ràng buộc về mặt quản lý dự án</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -485,16 +485,16 @@
         <v>Khả năng thanh toán qua thẻ tín dụng của cổng thanh toán điện tử — tính năng nghiệp vụ của hệ thống</v>
       </c>
       <c r="F3" t="str">
+        <v>Khả năng chịu tải và thời gian phản hồi của hệ thống dưới 2 giây — đặc tính vận hành và hiệu năng hệ thống</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Tính năng gửi email thông báo tự động cho khách hàng hằng ngày — hành vi xử lý dữ liệu của hệ thống</v>
+      </c>
+      <c r="H3" t="str">
         <v>Chức năng đăng nhập bằng vân tay của ứng dụng di động — tính năng bảo mật người dùng cụ thể</v>
       </c>
-      <c r="G3" t="str">
-        <v>Khả năng chịu tải và thời gian phản hồi của hệ thống dưới 2 giây — đặc tính vận hành và hiệu năng hệ thống</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Tính năng gửi email thông báo tự động cho khách hàng hằng ngày — hành vi xử lý dữ liệu của hệ thống</v>
-      </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Bảng câu hỏi khảo sát (Survey) là công cụ tối ưu để thu thập phản hồi nhanh chóng và định lượng từ số lượng lớn đối tượng.</v>
       </c>
       <c r="E4" t="str">
+        <v>Tạo bản mẫu (Prototyping) — thiết kế giao diện thử nghiệm để người dùng tương tác</v>
+      </c>
+      <c r="F4" t="str">
         <v>Phỏng vấn sâu (In-depth Interview) — tiếp cận từng cá nhân để lấy phản hồi chi tiết</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Bảng câu hỏi khảo sát (Survey/Questionnaire) — gửi câu hỏi định sẵn để thu thập dữ liệu định lượng lớn</v>
       </c>
       <c r="G4" t="str">
         <v>Quan sát trực tiếp (Observation) — theo dõi hành vi làm việc thực tế của người dùng</v>
       </c>
       <c r="H4" t="str">
-        <v>Tạo bản mẫu (Prototyping) — thiết kế giao diện thử nghiệm để người dùng tương tác</v>
+        <v>Bảng câu hỏi khảo sát (Survey/Questionnaire) — gửi câu hỏi định sẵn để thu thập dữ liệu định lượng lớn</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>User Story chuẩn có định dạng: "As a [role], I want [action], so that [benefit]" giúp tập trung vào đối tượng và giá trị thực tế mang lại.</v>
       </c>
       <c r="E5" t="str">
-        <v>Với tư cách là [vai trò], tôi muốn [chức năng], để [lợi ích] — định dạng chuẩn tập trung vào giá trị người dùng</v>
+        <v>Nếu [điều kiện] xảy ra thì [kết quả] phải hiển thị trên [giao diện] — định dạng rẽ nhánh điều kiện</v>
       </c>
       <c r="F5" t="str">
         <v>Hệ thống phải thực hiện [chức năng] cho [đối tượng] tại [thời điểm] — định dạng kỹ thuật hệ thống</v>
       </c>
       <c r="G5" t="str">
-        <v>Nếu [điều kiện] xảy ra thì [kết quả] phải hiển thị trên [giao diện] — định dạng rẽ nhánh điều kiện</v>
+        <v>Với tư cách là [vai trò], tôi muốn [chức năng], để [lợi ích] — định dạng chuẩn tập trung vào giá trị người dùng</v>
       </c>
       <c r="H5" t="str">
         <v>Nhà phát triển cần lập trình [tính năng] bằng cách sử dụng [công nghệ] — định dạng hướng triển khai kỹ thuật</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -598,19 +598,19 @@
         <v>MoSCoW viết tắt của Must have, Should have, Could have, và Won't have, là kỹ thuật phổ biến để sắp xếp độ ưu tiên yêu cầu.</v>
       </c>
       <c r="E7" t="str">
+        <v>Kiểm tra tính đúng đắn về mặt logic của các biểu đồ quy trình nghiệp vụ — xác thực luồng nghiệp vụ</v>
+      </c>
+      <c r="F7" t="str">
         <v>Sắp xếp thứ tự ưu tiên của các yêu cầu theo các mức độ quan trọng — phân loại Must, Should, Could, Won't</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>Ước lượng độ phức tạp và kích thước của yêu cầu bằng điểm câu chuyện — đo lường Story Points</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Kiểm tra tính đúng đắn về mặt logic của các biểu đồ quy trình nghiệp vụ — xác thực luồng nghiệp vụ</v>
       </c>
       <c r="H7" t="str">
         <v>Theo dõi tiến độ phát triển của các tính năng trên bảng Kanban — quản lý trạng thái công việc</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -627,10 +627,10 @@
         <v>Ngôn ngữ Gherkin định nghĩa kịch bản kiểm thử bằng cách thiết lập bối cảnh (Given), hành động kích hoạt (When) và kết quả hiển thị (Then).</v>
       </c>
       <c r="E8" t="str">
+        <v>Start (Bắt đầu) - Process (Xử lý) - End (Kết thúc) — cấu trúc luồng tuần tự của thuật toán</v>
+      </c>
+      <c r="F8" t="str">
         <v>Given (Bối cảnh) - When (Hành động) - Then (Kết quả mong đợi) — cấu trúc chuẩn mô tả kịch bản hành vi</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Start (Bắt đầu) - Process (Xử lý) - End (Kết thúc) — cấu trúc luồng tuần tự của thuật toán</v>
       </c>
       <c r="G8" t="str">
         <v>Input (Đầu vào) - Output (Đầu ra) - Validate (Xác thực) — cấu trúc kiểm tra dữ liệu kỹ thuật</v>
@@ -639,7 +639,7 @@
         <v>If (Nếu) - Then (Thì) - Else (Ngược lại) — cấu trúc câu lệnh điều kiện lập trình</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -662,10 +662,10 @@
         <v>Product Owner (PO) — người đại diện cho khách hàng và quản lý giá trị sản phẩm</v>
       </c>
       <c r="G9" t="str">
+        <v>Tech Lead — người chịu trách nhiệm về kiến trúc kỹ thuật và phân chia task lập trình</v>
+      </c>
+      <c r="H9" t="str">
         <v>Business Analyst (BA) — người viết tài liệu đặc tả và phân tích nghiệp vụ chi tiết</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Tech Lead — người chịu trách nhiệm về kiến trúc kỹ thuật và phân chia task lập trình</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -685,10 +685,10 @@
         <v>Ma trận Value vs Effort (2x2) giúp BA nhanh chóng phân loại yêu cầu để chọn ra những tính năng mang lại giá trị cao với nỗ lực thấp (Quick Wins).</v>
       </c>
       <c r="E10" t="str">
+        <v>Ma trận 2x2 Value vs Effort — phân loại tính năng vào các nhóm Quick Wins, Major Projects, Fill-ins, Thankless Tasks</v>
+      </c>
+      <c r="F10" t="str">
         <v>Ma trận RICE (Reach - Impact - Confidence - Effort) — tính điểm ưu tiên dựa trên 4 chỉ số định lượng</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Ma trận 2x2 Value vs Effort — phân loại tính năng vào các nhóm Quick Wins, Major Projects, Fill-ins, Thankless Tasks</v>
       </c>
       <c r="G10" t="str">
         <v>Phân tích SWOT (Strengths - Weaknesses - Opportunities - Threats) — phân tích chiến lược doanh nghiệp</v>
@@ -697,7 +697,7 @@
         <v>Ma trận RACI (Responsible - Accountable - Consulted - Informed) — phân chia trách nhiệm nhân sự</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>INVEST stands for: Independent, Negotiable, Valuable, Estimable (ước lượng được), Small, Testable.</v>
       </c>
       <c r="E11" t="str">
+        <v>Essential — Tính năng phải cực kỳ quan trọng và bắt buộc phải có trong sản phẩm</v>
+      </c>
+      <c r="F11" t="str">
+        <v>External — Story phải tập trung vào tương tác bên ngoài thay vì hệ thống nội bộ</v>
+      </c>
+      <c r="G11" t="str">
         <v>Estimable — Story phải có khả năng ước lượng được độ phức tạp bởi đội phát triển</v>
       </c>
-      <c r="F11" t="str">
+      <c r="H11" t="str">
         <v>Efficient — Tính năng phát triển phải đạt hiệu quả vận hành tối đa</v>
       </c>
-      <c r="G11" t="str">
-        <v>Essential — Tính năng phải cực kỳ quan trọng và bắt buộc phải có trong sản phẩm</v>
-      </c>
-      <c r="H11" t="str">
-        <v>External — Story phải tập trung vào tương tác bên ngoài thay vì hệ thống nội bộ</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Khi có Change Request, BA phải thực hiện phân tích tác động (Impact Analysis) để hiểu rõ thay đổi này ảnh hưởng thế nào đến các ràng buộc dự án trước khi đưa ra quyết định.</v>
       </c>
       <c r="E12" t="str">
-        <v>Cập nhật ngay vào code và báo Dev làm theo yêu cầu mới của khách hàng — hỗ trợ khách hàng nhanh chóng</v>
+        <v>Phân tích tác động (Impact Analysis) của thay đổi đối với phạm vi, tiến độ, chi phí và rủi ro của dự án — đánh giá ảnh hưởng</v>
       </c>
       <c r="F12" t="str">
         <v>Từ chối ngay lập tức vì dự án đã chốt scope và đang chạy dở sprint — bảo vệ phạm vi dự án ban đầu</v>
       </c>
       <c r="G12" t="str">
-        <v>Phân tích tác động (Impact Analysis) của thay đổi đối với phạm vi, tiến độ, chi phí và rủi ro của dự án — đánh giá ảnh hưởng</v>
+        <v>Cập nhật ngay vào code và báo Dev làm theo yêu cầu mới của khách hàng — hỗ trợ khách hàng nhanh chóng</v>
       </c>
       <c r="H12" t="str">
         <v>Yêu cầu khách hàng tự viết đặc tả chi tiết cho thay đổi đó rồi mới xử lý — giảm thiểu tải công việc cho BA</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -775,13 +775,13 @@
         <v>Business Requirement phản ánh mục tiêu chiến lược của tổ chức; User Requirement mô tả nhu cầu thực tế của người dùng khi dùng hệ thống</v>
       </c>
       <c r="F13" t="str">
+        <v>Business Requirement chỉ áp dụng cho dự án lớn; User Requirement áp dụng cho dự án nhỏ</v>
+      </c>
+      <c r="G13" t="str">
         <v>Business Requirement do Dev viết; User Requirement do BA viết tài liệu và kiểm thử</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Business Requirement mô tả chi tiết chức năng phần mềm; User Requirement mô tả giao diện màn hình</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Business Requirement chỉ áp dụng cho dự án lớn; User Requirement áp dụng cho dự án nhỏ</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -801,19 +801,19 @@
         <v>Focus Group thu thập phản hồi định tính của đối tượng mục tiêu về ý tưởng/sản phẩm. Workshop là cuộc họp cộng tác thiết kế để chốt yêu cầu cụ thể.</v>
       </c>
       <c r="E14" t="str">
+        <v>Focus Group bắt buộc phải có sự tham gia của Dev; Workshop chỉ dành riêng cho khách hàng và BA</v>
+      </c>
+      <c r="F14" t="str">
         <v>Focus Group nhằm thu thập cảm nhận, ý kiến chủ quan về sản phẩm; Workshop nhằm thảo luận sâu để đạt sự đồng thuận về yêu cầu kỹ thuật</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Focus Group kéo dài nhiều ngày liên tục; Workshop chỉ diễn ra trong vòng 1-2 tiếng</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Focus Group bắt buộc phải có sự tham gia của Dev; Workshop chỉ dành riêng cho khách hàng và BA</v>
       </c>
       <c r="H14" t="str">
         <v>Focus Group dùng để vẽ sơ đồ quy trình; Workshop dùng để kiểm thử lỗi hệ thống</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Requirement Traceability Matrix (RTM) giúp đảm bảo tính thông suốt từ Business Requirement -&gt; User Story -&gt; Design -&gt; Code -&gt; Test Case, kiểm soát scope creep.</v>
       </c>
       <c r="E15" t="str">
+        <v>Sơ đồ Use Case tổng thể dự án — sơ đồ thể hiện mối quan hệ giữa Actor và chức năng</v>
+      </c>
+      <c r="F15" t="str">
         <v>Bảng ma trận truy vết yêu cầu (Requirement Traceability Matrix - RTM) — công cụ ánh xạ yêu cầu từ đầu đến cuối</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>Biểu đồ phân rã chức năng (Functional Decomposition Diagram) — sơ đồ chia nhỏ hệ thống thành module</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Sơ đồ Use Case tổng thể dự án — sơ đồ thể hiện mối quan hệ giữa Actor và chức năng</v>
       </c>
       <c r="H15" t="str">
         <v>Bảng kế hoạch giải phóng sản phẩm (Release Plan) — lịch trình bàn giao tính năng</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Confidence (Độ tin cậy) là tỷ lệ phần trăm (ví dụ: 100% cực kỳ tin cậy, 50% phỏng đoán) giúp điều chỉnh điểm ưu tiên dựa trên mức độ dữ liệu thực chứng.</v>
       </c>
       <c r="E16" t="str">
+        <v>Mức độ tác động tích cực của tính năng đối với trải nghiệm người dùng hoặc chuyển đổi số</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Số lượng developer tự tin có thể lập trình thành công tính năng mà không phát sinh bug</v>
+      </c>
+      <c r="G16" t="str">
         <v>Mức độ tự tin của BA về độ chính xác của các ước tính về Reach, Impact và Effort dựa trên dữ liệu hiện có</v>
       </c>
-      <c r="F16" t="str">
+      <c r="H16" t="str">
         <v>Số lượng người dùng mà tính năng sẽ tiếp cận được trong một khoảng thời gian nhất định</v>
       </c>
-      <c r="G16" t="str">
-        <v>Mức độ tác động tích cực của tính năng đối với trải nghiệm người dùng hoặc chuyển đổi số</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Số lượng developer tự tin có thể lập trình thành công tính năng mà không phát sinh bug</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Phân rã theo chiều dọc (Vertical Slicing) đảm bảo mỗi story con đều chứa đầy đủ các tầng để hoạt động được và mang lại giá trị nghiệm thu độc lập cho người dùng.</v>
       </c>
       <c r="E17" t="str">
+        <v>Phân chia theo các lát cắt giá trị nghiệp vụ có thể chạy được từ đầu đến cuối (Vertical Slicing) — đảm bảo mỗi story nhỏ vẫn bàn giao được giá trị thực tế</v>
+      </c>
+      <c r="F17" t="str">
         <v>Phân chia theo cấu trúc kỹ thuật hệ thống (ví dụ: tạo 1 story cho Database, 1 story cho Frontend, 1 story cho Backend) — phân chia theo layer</v>
       </c>
-      <c r="F17" t="str">
-        <v>Phân chia theo các lát cắt giá trị nghiệp vụ có thể chạy được từ đầu đến cuối (Vertical Slicing) — đảm bảo mỗi story nhỏ vẫn bàn giao được giá trị thực tế</v>
-      </c>
       <c r="G17" t="str">
+        <v>Phân chia theo thứ tự bảng chữ cái của các trường dữ liệu trên màn hình đăng ký thông tin — phân chia theo UI elements</v>
+      </c>
+      <c r="H17" t="str">
         <v>Phân chia dựa trên năng lực và số lượng lập trình viên có sẵn trong đội phát triển — phân chia theo headcount</v>
       </c>
-      <c r="H17" t="str">
-        <v>Phân chia theo thứ tự bảng chữ cái của các trường dữ liệu trên màn hình đăng ký thông tin — phân chia theo UI elements</v>
-      </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Story quá lớn (Epic/21 points) chứa nhiều sự không chắc chắn và rủi ro. BA cần hỗ trợ PO làm rõ nghiệp vụ và phân rã thành các story nhỏ hơn để đưa vào sprint.</v>
       </c>
       <c r="E18" t="str">
+        <v>Chuyển Story đó sang Sprint tiếp theo và thay thế bằng các task sửa lỗi nhỏ hơn — trì hoãn xử lý</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Đề xuất làm rõ và phân rã (split) Story đó thành các Story nhỏ hơn có độ phức tạp thấp hơn (dưới 8 points) — giúp dễ kiểm soát phạm vi và bàn giao</v>
+      </c>
+      <c r="G18" t="str">
         <v>Yêu cầu Dev giải thích chi tiết code và ép họ giảm điểm ước lượng xuống mức thấp hơn — tối ưu hóa năng suất team</v>
       </c>
-      <c r="F18" t="str">
+      <c r="H18" t="str">
         <v>Giữ nguyên story đó và chia đều công việc cho nhiều lập trình viên cùng vào code chung một lúc — giải quyết tài nguyên</v>
       </c>
-      <c r="G18" t="str">
-        <v>Đề xuất làm rõ và phân rã (split) Story đó thành các Story nhỏ hơn có độ phức tạp thấp hơn (dưới 8 points) — giúp dễ kiểm soát phạm vi và bàn giao</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Chuyển Story đó sang Sprint tiếp theo và thay thế bằng các task sửa lỗi nhỏ hơn — trì hoãn xử lý</v>
-      </c>
       <c r="I18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>BA đóng vai trò cầu nối giải quyết xung đột bằng cách điều phối họp dựa trên dữ liệu thực tế, cân đối giữa trải nghiệm người dùng (UX) và mục tiêu kinh doanh cốt lõi.</v>
       </c>
       <c r="E19" t="str">
+        <v>Yêu cầu hai bên tự thỏa thuận ngoài giờ, khi nào chốt xong giải pháp thì báo lại cho BA cập nhật tài liệu — giảm trách nhiệm trung gian</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Thực hiện cả hai yêu cầu cùng lúc bằng cách thiết kế popup quảng cáo ẩn hiện luân phiên ở từng bước thanh toán — thỏa hiệp cơ học</v>
+      </c>
+      <c r="G19" t="str">
         <v>Lắng nghe bộ phận nào có quyền lực cao hơn trong công ty và làm theo yêu cầu của họ — tuân thủ phân cấp tổ chức</v>
       </c>
-      <c r="F19" t="str">
+      <c r="H19" t="str">
         <v>Tổ chức họp cộng tác phân tích tác động (Impact Analysis), đưa ra dữ liệu thực tế (Analytics/A-B testing) và hướng tới mục tiêu kinh doanh tối thượng của sản phẩm — tìm giải pháp cân bằng dựa trên dữ liệu</v>
       </c>
-      <c r="G19" t="str">
-        <v>Thực hiện cả hai yêu cầu cùng lúc bằng cách thiết kế popup quảng cáo ẩn hiện luân phiên ở từng bước thanh toán — thỏa hiệp cơ học</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Yêu cầu hai bên tự thỏa thuận ngoài giờ, khi nào chốt xong giải pháp thì báo lại cho BA cập nhật tài liệu — giảm trách nhiệm trung gian</v>
-      </c>
       <c r="I19">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -978,16 +978,16 @@
         <v>Câu trên hoàn toàn tốt và sẵn sàng chuyển giao cho đội phát triển vì rất ngắn gọn và dễ hiểu</v>
       </c>
       <c r="F20" t="str">
+        <v>Yêu cầu quá chi tiết về mặt kỹ thuật — BA không nên đề cập đến từ "phản hồi" hay "tải cao"</v>
+      </c>
+      <c r="G20" t="str">
         <v>Yêu cầu vi phạm tính đo lường được (Measurable) — cần định nghĩa rõ thời gian phản hồi (ví dụ: latency &lt; 2s) và tải cao là bao nhiêu (ví dụ: 10,000 active users)</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Yêu cầu vi phạm tính khả thi (Feasible) — vì hệ thống không thể phản hồi nhanh dưới tải cao</v>
       </c>
-      <c r="H20" t="str">
-        <v>Yêu cầu quá chi tiết về mặt kỹ thuật — BA không nên đề cập đến từ "phản hồi" hay "tải cao"</v>
-      </c>
       <c r="I20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Theo ma trận Value/Effort, các tính năng nỗ lực cao nhưng giá trị thấp được coi là "Thankless Tasks" hoặc "Money Pits", nên từ chối hoặc trì hoãn để ưu tiên Quick Wins.</v>
       </c>
       <c r="E21" t="str">
+        <v>Chuyển tính năng này cho đội phát triển tự nghiên cứu ngoài giờ để tiết kiệm thời gian chạy dự án chính thức — tận dụng tài nguyên</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Cắt nhỏ tính năng ra thành 10 phần bằng nhau và đưa rải rác vào mỗi sprint để khách hàng không nhận ra sự chậm trễ — phân phối tải</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Thuyết phục PO đặt tính năng này vào nhóm "Won't Have" hoặc trì hoãn xuống cuối Product Backlog, giải thích rõ nỗ lực so với giá trị thu về để tìm giải pháp thay thế đơn giản hơn — quản lý phạm vi hiệu quả</v>
+      </c>
+      <c r="H21" t="str">
         <v>Đưa vào phát triển ngay ở Sprint tiếp theo vì khách hàng là thượng đế — tối ưu hóa sự hài lòng tức thời</v>
       </c>
-      <c r="F21" t="str">
-        <v>Thuyết phục PO đặt tính năng này vào nhóm "Won't Have" hoặc trì hoãn xuống cuối Product Backlog, giải thích rõ nỗ lực so với giá trị thu về để tìm giải pháp thay thế đơn giản hơn — quản lý phạm vi hiệu quả</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Chuyển tính năng này cho đội phát triển tự nghiên cứu ngoài giờ để tiết kiệm thời gian chạy dự án chính thức — tận dụng tài nguyên</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Cắt nhỏ tính năng ra thành 10 phần bằng nhau và đưa rải rác vào mỗi sprint để khách hàng không nhận ra sự chậm trễ — phân phối tải</v>
-      </c>
       <c r="I21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Hệ thống cũ thường bị mất mát tài liệu. BA phải chủ động dùng kỹ thuật Reverse Engineering thông qua phân tích dữ liệu hiện có và phỏng vấn nghiệp vụ để tái thiết lập yêu cầu.</v>
       </c>
       <c r="E22" t="str">
+        <v>Cơ sở hạ tầng mạng của khách hàng quá yếu — Giải pháp: Đề xuất khách hàng nâng cấp toàn bộ hệ thống máy chủ vật lý</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Khách hàng không muốn đổi sang hệ thống mới — Giải pháp: BA tự ý chốt toàn bộ tính năng mới mà không cần lấy ý kiến khách hàng</v>
+      </c>
+      <c r="G22" t="str">
         <v>Thiếu tài liệu đặc tả của hệ thống cũ — Giải pháp: BA cần thực hiện đảo ngược kỹ nghệ (Reverse Engineering) qua đọc cấu trúc database, quan sát thực tế và phỏng vấn người dùng lâu năm</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v>Lập trình viên không muốn đọc tài liệu cũ — Giải pháp: BA tự code thay lập trình viên các phần khó để đẩy nhanh tiến độ</v>
       </c>
-      <c r="G22" t="str">
-        <v>Khách hàng không muốn đổi sang hệ thống mới — Giải pháp: BA tự ý chốt toàn bộ tính năng mới mà không cần lấy ý kiến khách hàng</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Cơ sở hạ tầng mạng của khách hàng quá yếu — Giải pháp: Đề xuất khách hàng nâng cấp toàn bộ hệ thống máy chủ vật lý</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1065,16 +1065,16 @@
         <v>Mô tả các màn hình UI/UX chi tiết từ màu sắc nút bấm đến font chữ hiển thị</v>
       </c>
       <c r="F23" t="str">
+        <v>Yêu cầu lập trình viên tự nghiên cứu các kịch bản lỗi vì đó là nhiệm vụ kỹ thuật</v>
+      </c>
+      <c r="G23" t="str">
         <v>Sử dụng định dạng Scenario-based với Given-When-Then bao phủ cả luồng chính (Happy Path) và các luồng ngoại lệ/lỗi thanh toán (Edge Cases/Alternative Paths)</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>Viết một danh sách các công nghệ API cần gọi và cấu trúc dữ liệu lưu trong bảng Database</v>
       </c>
-      <c r="H23" t="str">
-        <v>Yêu cầu lập trình viên tự nghiên cứu các kịch bản lỗi vì đó là nhiệm vụ kỹ thuật</v>
-      </c>
       <c r="I23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Traceability liên kết yêu cầu đầu vào với các sản phẩm đầu ra (code, test). Điều này giúp kiểm soát scope creep và đánh giá tác động của thay đổi (Change Impact Analysis) một cách toàn diện.</v>
       </c>
       <c r="E24" t="str">
-        <v>Để đảm bảo không có yêu cầu nào bị bỏ sót trong quá trình code/test, đồng thời đánh giá chính xác tác động khi có một yêu cầu thay đổi đột xuất</v>
+        <v>Để quản lý thời gian làm việc hàng ngày của từng lập trình viên trong đội phát triển</v>
       </c>
       <c r="F24" t="str">
         <v>Để tự động hóa việc sinh code từ các câu chữ yêu cầu của khách hàng mà không cần lập trình viên can thiệp</v>
       </c>
       <c r="G24" t="str">
-        <v>Để quản lý thời gian làm việc hàng ngày của từng lập trình viên trong đội phát triển</v>
+        <v>Để đảm bảo không có yêu cầu nào bị bỏ sót trong quá trình code/test, đồng thời đánh giá chính xác tác động khi có một yêu cầu thay đổi đột xuất</v>
       </c>
       <c r="H24" t="str">
         <v>Để chứng minh lỗi phát sinh là do khách hàng yêu cầu sai chứ không phải do lỗi của đội phát triển</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Trong Sprint, scope của Sprint Backlog được bảo vệ để đảm bảo team tập trung hoàn thành Sprint Goal. Thay đổi yêu cầu giữa chừng phải được PO đánh giá tác động, nếu break Sprint Goal thì có thể từ chối và đưa vào backlog cho sprint sau.</v>
       </c>
       <c r="E25" t="str">
-        <v>Đồng ý và yêu cầu Dev sửa code ngay vì đang chạy Agile nên phải thích ứng với thay đổi bất kỳ lúc nào — hiểu sai về linh hoạt của Agile</v>
+        <v>Cùng PO thảo luận với đội phát triển để đánh giá độ phức tạp; nếu thay đổi quá lớn làm ảnh hưởng đến Sprint Goal, đề xuất đưa thay đổi này vào Product Backlog để lập kế hoạch cho Sprint sau</v>
       </c>
       <c r="F25" t="str">
-        <v>Cùng PO thảo luận với đội phát triển để đánh giá độ phức tạp; nếu thay đổi quá lớn làm ảnh hưởng đến Sprint Goal, đề xuất đưa thay đổi này vào Product Backlog để lập kế hoạch cho Sprint sau</v>
+        <v>Hủy bỏ toàn bộ Sprint hiện tại ngay lập tức để thiết lập lại cuộc họp kế hoạch Sprint mới</v>
       </c>
       <c r="G25" t="str">
         <v>Từ chối thẳng thừng và không báo lại cho PO biết vì việc sửa đổi trong sprint là cấm kỵ tuyệt đối</v>
       </c>
       <c r="H25" t="str">
-        <v>Hủy bỏ toàn bộ Sprint hiện tại ngay lập tức để thiết lập lại cuộc họp kế hoạch Sprint mới</v>
+        <v>Đồng ý và yêu cầu Dev sửa code ngay vì đang chạy Agile nên phải thích ứng với thay đổi bất kỳ lúc nào — hiểu sai về linh hoạt của Agile</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Để yêu cầu test được, BA phải lượng hóa bằng các chỉ số kỹ thuật cụ thể (ví dụ: dưới 1.5 giây ở mức tải 100 requests/s) làm căn cứ kỹ thuật rõ ràng.</v>
       </c>
       <c r="E26" t="str">
+        <v>Yêu cầu QA tự định nghĩa thế nào là "nhanh chóng" để phục vụ việc viết test case hiệu năng</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Xóa bỏ hoàn toàn yêu cầu này ra khỏi tài liệu vì hiệu năng tải trang là việc của đội vận hành hạ tầng</v>
+      </c>
+      <c r="G26" t="str">
         <v>Giải thích với QA rằng "nhanh chóng" nghĩa là người dùng cảm thấy không bị lag, không cần viết chỉ số cụ thể</v>
       </c>
-      <c r="F26" t="str">
+      <c r="H26" t="str">
         <v>Chuyển đổi yêu cầu thành: "Trang quản trị phải hoàn thành việc render toàn bộ dữ liệu (Time to Interactive) dưới 1.5 giây trong điều kiện tải bình thường (dưới 100 requests/giây)"</v>
       </c>
-      <c r="G26" t="str">
-        <v>Yêu cầu QA tự định nghĩa thế nào là "nhanh chóng" để phục vụ việc viết test case hiệu năng</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Xóa bỏ hoàn toàn yêu cầu này ra khỏi tài liệu vì hiệu năng tải trang là việc của đội vận hành hạ tầng</v>
-      </c>
       <c r="I26">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
